--- a/artfynd/A 60716-2021 artfynd.xlsx
+++ b/artfynd/A 60716-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60716-2021 artfynd.xlsx
+++ b/artfynd/A 60716-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97383944</v>
+        <v>97383937</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371223.8177090761</v>
+        <v>371135</v>
       </c>
       <c r="R2" t="n">
-        <v>6744653.964307282</v>
+        <v>6744809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97383905</v>
+        <v>97383924</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371104.6060876616</v>
+        <v>371151</v>
       </c>
       <c r="R3" t="n">
-        <v>6744765.694054871</v>
+        <v>6744579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97383937</v>
+        <v>97383912</v>
       </c>
       <c r="B4" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>371135.0265551978</v>
+        <v>371300</v>
       </c>
       <c r="R4" t="n">
-        <v>6744809.02867246</v>
+        <v>6744770</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97383922</v>
+        <v>97383944</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>371221.313728622</v>
+        <v>371224</v>
       </c>
       <c r="R5" t="n">
-        <v>6744625.24492522</v>
+        <v>6744654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97383934</v>
+        <v>97383910</v>
       </c>
       <c r="B6" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>371002.8556096497</v>
+        <v>370947</v>
       </c>
       <c r="R6" t="n">
-        <v>6744724.449491068</v>
+        <v>6744603</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97383928</v>
+        <v>97383917</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>371053.1167658683</v>
+        <v>371158</v>
       </c>
       <c r="R7" t="n">
-        <v>6744734.839612942</v>
+        <v>6744584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97383925</v>
+        <v>97383905</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370939.4954976452</v>
+        <v>371104</v>
       </c>
       <c r="R8" t="n">
-        <v>6744676.446748036</v>
+        <v>6744765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97383910</v>
+        <v>97383920</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>370947.5950156241</v>
+        <v>370953</v>
       </c>
       <c r="R9" t="n">
-        <v>6744602.908073967</v>
+        <v>6744673</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97383930</v>
+        <v>97383927</v>
       </c>
       <c r="B10" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>371174.3428833798</v>
+        <v>370940</v>
       </c>
       <c r="R10" t="n">
-        <v>6744597.642494702</v>
+        <v>6744672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97383908</v>
+        <v>97383931</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>370947.5950156241</v>
+        <v>371070</v>
       </c>
       <c r="R11" t="n">
-        <v>6744602.908073967</v>
+        <v>6744731</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97383921</v>
+        <v>97383903</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>371001.0552476444</v>
+        <v>371149</v>
       </c>
       <c r="R12" t="n">
-        <v>6744715.237031102</v>
+        <v>6744584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97383933</v>
+        <v>97383930</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>371074.0237595745</v>
+        <v>371175</v>
       </c>
       <c r="R13" t="n">
-        <v>6744569.038105329</v>
+        <v>6744597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97383909</v>
+        <v>103540879</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,37 +1850,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nybännan, norr om, Vrm</t>
+          <t>Nybrännan, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>370947.5950156241</v>
+        <v>371201</v>
       </c>
       <c r="R14" t="n">
-        <v>6744602.908073967</v>
+        <v>6744591</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +1905,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97383935</v>
+        <v>97383934</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +1958,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>371082.9162868222</v>
+        <v>371003</v>
       </c>
       <c r="R15" t="n">
-        <v>6744747.43465819</v>
+        <v>6744724</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2015,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2044,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97383912</v>
+        <v>103540854</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,37 +2055,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nybännan, norr om, Vrm</t>
+          <t>Nybrännan , Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>371300.3829165885</v>
+        <v>371196</v>
       </c>
       <c r="R16" t="n">
-        <v>6744769.855884247</v>
+        <v>6744624</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2313,22 +2110,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,53 +2152,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97383936</v>
+        <v>103540986</v>
       </c>
       <c r="B17" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nybännan, norr om, Vrm</t>
+          <t>Nybrännan , Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>371082.9162868222</v>
+        <v>371034</v>
       </c>
       <c r="R17" t="n">
-        <v>6744747.43465819</v>
+        <v>6744523</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,22 +2218,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-11-23</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2260,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97383907</v>
+        <v>97383909</v>
       </c>
       <c r="B18" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>370947.5950156241</v>
+        <v>370947</v>
       </c>
       <c r="R18" t="n">
-        <v>6744602.908073967</v>
+        <v>6744603</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2328,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2357,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97383927</v>
+        <v>97383918</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,21 +2368,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2392,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>370939.8427982506</v>
+        <v>371073</v>
       </c>
       <c r="R19" t="n">
-        <v>6744672.527785623</v>
+        <v>6744566</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,19 +2425,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2454,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97383918</v>
+        <v>97383921</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,10 +2489,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>371072.9410990948</v>
+        <v>371001</v>
       </c>
       <c r="R20" t="n">
-        <v>6744566.147355751</v>
+        <v>6744715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2764,19 +2522,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2551,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97383920</v>
+        <v>97383925</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2562,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>370952.5599609155</v>
+        <v>370940</v>
       </c>
       <c r="R21" t="n">
-        <v>6744672.55602329</v>
+        <v>6744677</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2876,19 +2619,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2648,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97383943</v>
+        <v>97383928</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2683,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>371173.7969547142</v>
+        <v>371053</v>
       </c>
       <c r="R22" t="n">
-        <v>6744582.524645166</v>
+        <v>6744735</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2988,19 +2716,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,37 +2745,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97383926</v>
+        <v>97383935</v>
       </c>
       <c r="B23" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2780,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>370939.4954976452</v>
+        <v>371083</v>
       </c>
       <c r="R23" t="n">
-        <v>6744676.446748036</v>
+        <v>6744747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,19 +2813,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2842,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97383923</v>
+        <v>97383908</v>
       </c>
       <c r="B24" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3179,10 +2877,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>371221.313728622</v>
+        <v>370947</v>
       </c>
       <c r="R24" t="n">
-        <v>6744625.24492522</v>
+        <v>6744603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3212,19 +2910,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,15 +2939,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97383942</v>
+        <v>97383923</v>
       </c>
       <c r="B25" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +2950,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>371173.7969547142</v>
+        <v>371221</v>
       </c>
       <c r="R25" t="n">
-        <v>6744582.524645166</v>
+        <v>6744625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3324,19 +3007,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,37 +3036,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97383931</v>
+        <v>97383926</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3071,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>371070.1062210795</v>
+        <v>370940</v>
       </c>
       <c r="R26" t="n">
-        <v>6744731.295787927</v>
+        <v>6744677</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3436,19 +3104,9 @@
           <t>2021-11-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-11-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,15 +3133,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103540815</v>
+        <v>97383943</v>
       </c>
       <c r="B27" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,38 +3144,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Nybrännan, Vrm</t>
+          <t>Nybännan, norr om, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>371189.5599479396</v>
+        <v>371174</v>
       </c>
       <c r="R27" t="n">
-        <v>6744612.718817585</v>
+        <v>6744582</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3546,22 +3198,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3588,15 +3230,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103540986</v>
+        <v>103540824</v>
       </c>
       <c r="B28" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3604,21 +3241,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6450</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3629,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>371033.70795377</v>
+        <v>371196</v>
       </c>
       <c r="R28" t="n">
-        <v>6744522.640346987</v>
+        <v>6744624</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3664,7 +3301,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3674,7 +3311,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,15 +3338,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103540854</v>
+        <v>97383919</v>
       </c>
       <c r="B29" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,38 +3349,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6450</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nybrännan , Vrm</t>
+          <t>Nybännan, norr om, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>371196.3147856223</v>
+        <v>371156</v>
       </c>
       <c r="R29" t="n">
-        <v>6744623.705926095</v>
+        <v>6744574</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3772,22 +3412,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3796,6 +3426,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3814,15 +3445,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103540824</v>
+        <v>97383904</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3830,38 +3456,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Nybrännan , Vrm</t>
+          <t>Nybännan, norr om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>371196.3147856223</v>
+        <v>371064</v>
       </c>
       <c r="R30" t="n">
-        <v>6744623.705926095</v>
+        <v>6744573</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3885,22 +3510,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,6 +3539,599 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>97383907</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nybännan, norr om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>370947</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6744603</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97383922</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nybännan, norr om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>371221</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6744625</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97383933</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nybännan, norr om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>371074</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6744569</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>97383936</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nybännan, norr om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>371083</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6744747</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>97383942</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nybännan, norr om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>371174</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6744582</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-11-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>103540815</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nybrännan, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>371190</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6744612</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60716-2021 artfynd.xlsx
+++ b/artfynd/A 60716-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383937</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383924</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383944</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383910</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383917</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383905</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383920</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383927</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383931</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383903</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1944,6 +2009,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103540879</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2041,6 +2111,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383934</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2149,6 +2224,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103540854</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2257,6 +2337,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103540986</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2354,6 +2439,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383909</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383918</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2548,6 +2643,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383921</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2645,6 +2745,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383925</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2742,6 +2847,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383928</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2839,6 +2949,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383935</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2936,6 +3051,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383908</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3033,6 +3153,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383923</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3130,6 +3255,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383926</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3227,6 +3357,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383943</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3335,6 +3470,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103540824</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3442,6 +3582,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383919</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3539,6 +3684,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383904</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3636,6 +3786,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383907</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3733,6 +3888,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383922</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3830,6 +3990,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383933</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3927,6 +4092,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383936</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4024,6 +4194,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97383942</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4132,8 +4307,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103540815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>